--- a/history_prices/MAR/prices_09032026.xlsx
+++ b/history_prices/MAR/prices_09032026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\MAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343889BD-7F6B-4F9F-AE97-DBE04CCAA883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB34014-6DDA-4184-AC84-29863F18368D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -279,9 +279,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -314,9 +314,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
